--- a/data/berita_antara_2026-07-30.xlsx
+++ b/data/berita_antara_2026-07-30.xlsx
@@ -471,99 +471,99 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>politik</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20 ide tema 17 Agustus 2026 yang kreatif, unik, dan penuh makna untuk HUT ke-81 RI</t>
+          <t>IHSG Kamis dibuka menguat 18,89 poin ke posisi 6.110</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 23:34:21 +0700</t>
+          <t>Thu, 30 Jul 2026 09:04:15 +0700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 tinggal menghitung hari. ...</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis pagi, dibuka menguat 18,89 poin atau 0,31 ...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5673507/20-ide-tema-17-agustus-2026-yang-kreatif-unik-dan-penuh-makna-untuk-hut-ke-81-ri</t>
+          <t>https://www.antaranews.com/berita/5672037/ihsg-kamis-dibuka-menguat-1889-poin-ke-posisi-6110</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/IMG-20260630-WA0035.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-270726-dr-01.jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ekonomi, otomotif</t>
+          <t>politik</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6 titik shuttle bus gratis GIIAS 2026 ke ICE BSD, cek lokasi &amp; jadwalnya</t>
+          <t>20 ide tema 17 Agustus 2026 yang kreatif, unik, dan penuh makna untuk HUT ke-81 RI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 18:17:21 +0700</t>
+          <t>Thu, 30 Jul 2026 23:34:21 +0700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Penyelenggara GAIKINDO Indonesia International Auto Show (GIIAS) 2026 kembali menyediakan layanan shuttle bus gratis ...</t>
+          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 tinggal menghitung hari. ...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5672876/6-titik-shuttle-bus-gratis-giias-2026-ke-ice-bsd-cek-lokasi-jadwalnya</t>
+          <t>https://www.antaranews.com/berita/5673507/20-ide-tema-17-agustus-2026-yang-kreatif-unik-dan-penuh-makna-untuk-hut-ke-81-ri</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/IMG_1404.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/IMG-20260630-WA0035.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi, otomotif</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PU uji coba irigasi Pante Lhong Aceh untuk aliri 6.562 hektare sawah</t>
+          <t>6 titik shuttle bus gratis GIIAS 2026 ke ICE BSD, cek lokasi &amp; jadwalnya</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 17:28:11 +0700</t>
+          <t>Thu, 30 Jul 2026 18:17:21 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Menteri Pekerjaan Umum (PU) Dody Hanggodo melakukan uji coba irigasi Pante Lhong Kabupaten Bireuen, Aceh yang telah ...</t>
+          <t>Penyelenggara GAIKINDO Indonesia International Auto Show (GIIAS) 2026 kembali menyediakan layanan shuttle bus gratis ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672783/pu-uji-coba-irigasi-pante-lhong-aceh-untuk-aliri-6562-hektare-sawah</t>
+          <t>https://otomotif.antaranews.com/berita/5672876/6-titik-shuttle-bus-gratis-giias-2026-ke-ice-bsd-cek-lokasi-jadwalnya</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG-20260730-WA0014_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/IMG_1404.jpg</t>
         </is>
       </c>
     </row>
@@ -575,28 +575,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IHSG ditutup menguat ditopang musim laporan keuangan emiten</t>
+          <t>PU uji coba irigasi Pante Lhong Aceh untuk aliri 6.562 hektare sawah</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 17:05:56 +0700</t>
+          <t>Thu, 30 Jul 2026 17:28:11 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis sore ditutup menguat ditopang oleh musim ...</t>
+          <t>Menteri Pekerjaan Umum (PU) Dody Hanggodo melakukan uji coba irigasi Pante Lhong Kabupaten Bireuen, Aceh yang telah ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672741/ihsg-ditutup-menguat-ditopang-musim-laporan-keuangan-emiten</t>
+          <t>https://www.antaranews.com/berita/5672783/pu-uji-coba-irigasi-pante-lhong-aceh-untuk-aliri-6562-hektare-sawah</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/pembukaan-ihsg-usai-libur-lebaran-2760782.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG-20260730-WA0014_1.jpg</t>
         </is>
       </c>
     </row>
@@ -608,28 +608,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OJK tuntaskan pemeriksaan 17 kasus manipulasi di pasar modal</t>
+          <t>IHSG ditutup menguat ditopang musim laporan keuangan emiten</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:26:08 +0700</t>
+          <t>Thu, 30 Jul 2026 17:05:56 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan telah menyelesaikan pemeriksaan atas sebanyak 17 kasus terkait pelanggaran ...</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis sore ditutup menguat ditopang oleh musim ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672663/ojk-tuntaskan-pemeriksaan-17-kasus-manipulasi-di-pasar-modal</t>
+          <t>https://www.antaranews.com/berita/5672741/ihsg-ditutup-menguat-ditopang-musim-laporan-keuangan-emiten</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/WhatsApp-Image-2026-06-30-at-18.00.00.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/pembukaan-ihsg-usai-libur-lebaran-2760782.jpg</t>
         </is>
       </c>
     </row>
@@ -641,28 +641,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OJK ungkap 7 manajer investasi andil peluncuran ETF Emas di 10 Agustus</t>
+          <t>OJK tuntaskan pemeriksaan 17 kasus manipulasi di pasar modal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:07:07 +0700</t>
+          <t>Thu, 30 Jul 2026 16:26:08 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan sebanyak lima sampai tujuh Manajer Investasi (MI) akan turut berpartisipasi ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan telah menyelesaikan pemeriksaan atas sebanyak 17 kasus terkait pelanggaran ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672456/ojk-ungkap-7-manajer-investasi-andil-peluncuran-etf-emas-di-10-agustus</t>
+          <t>https://www.antaranews.com/berita/5672663/ojk-tuntaskan-pemeriksaan-17-kasus-manipulasi-di-pasar-modal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/06/IMG-20260406-WA0035_copy_1280x732.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/WhatsApp-Image-2026-06-30-at-18.00.00.jpeg</t>
         </is>
       </c>
     </row>
@@ -674,28 +674,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United Tractors cetak pendapatan Rp58,3 triliun di semester I-2026</t>
+          <t>OJK ungkap 7 manajer investasi andil peluncuran ETF Emas di 10 Agustus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 12:29:10 +0700</t>
+          <t>Thu, 30 Jul 2026 14:07:07 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Perusahaan grup PT Astra International Tbk (ASII) yaitu PT United Tractors Tbk (UNTR) membukukan pendapatan bersih ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan sebanyak lima sampai tujuh Manajer Investasi (MI) akan turut berpartisipasi ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672283/united-tractors-cetak-pendapatan-rp583-triliun-di-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5672456/ojk-ungkap-7-manajer-investasi-andil-peluncuran-etf-emas-di-10-agustus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/16/1000566369_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/06/IMG-20260406-WA0035_copy_1280x732.jpg</t>
         </is>
       </c>
     </row>
@@ -707,28 +707,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IHSG menguat dipicu "risk on" pasar seiring The Fed tahan suku bunga</t>
+          <t>United Tractors cetak pendapatan Rp58,3 triliun di semester I-2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 09:48:24 +0700</t>
+          <t>Thu, 30 Jul 2026 12:29:10 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis bergerak menguat dipicu oleh sikap risk ...</t>
+          <t>Perusahaan grup PT Astra International Tbk (ASII) yaitu PT United Tractors Tbk (UNTR) membukukan pendapatan bersih ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672087/ihsg-menguat-dipicu-risk-on-pasar-seiring-the-fed-tahan-suku-bunga</t>
+          <t>https://www.antaranews.com/berita/5672283/united-tractors-cetak-pendapatan-rp583-triliun-di-semester-i-2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-270726-dr-05.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/16/1000566369_1.jpg</t>
         </is>
       </c>
     </row>
@@ -740,28 +740,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IHSG Kamis dibuka menguat 18,89 poin ke posisi 6.110</t>
+          <t>IHSG menguat dipicu "risk on" pasar seiring The Fed tahan suku bunga</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 09:04:15 +0700</t>
+          <t>Thu, 30 Jul 2026 09:48:24 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis pagi, dibuka menguat 18,89 poin atau 0,31 ...</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis bergerak menguat dipicu oleh sikap risk ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672037/ihsg-kamis-dibuka-menguat-1889-poin-ke-posisi-6110</t>
+          <t>https://www.antaranews.com/berita/5672087/ihsg-menguat-dipicu-risk-on-pasar-seiring-the-fed-tahan-suku-bunga</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-270726-dr-01.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-270726-dr-05.jpg</t>
         </is>
       </c>
     </row>

--- a/data/berita_antara_2026-07-30.xlsx
+++ b/data/berita_antara_2026-07-30.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -429,6 +429,7 @@
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,6 +468,11 @@
           <t>URL Gambar</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,6 +506,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-270726-dr-01.jpg</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -533,6 +540,11 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/IMG-20260630-WA0035.jpg</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -566,6 +578,11 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/IMG_1404.jpg</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -599,6 +616,11 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG-20260730-WA0014_1.jpg</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -632,6 +654,11 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/pembukaan-ihsg-usai-libur-lebaran-2760782.jpg</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -665,6 +692,11 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/WhatsApp-Image-2026-06-30-at-18.00.00.jpeg</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -698,6 +730,11 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/04/06/IMG-20260406-WA0035_copy_1280x732.jpg</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -731,6 +768,11 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/04/16/1000566369_1.jpg</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -764,6 +806,11 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-270726-dr-05.jpg</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -797,9 +844,14 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/06/18/7297.jpg</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:H11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-07-30.xlsx
+++ b/data/berita_antara_2026-07-30.xlsx
@@ -511,33 +511,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>politik</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20 ide tema 17 Agustus 2026 yang kreatif, unik, dan penuh makna untuk HUT ke-81 RI</t>
+          <t>IHSG menguat dipicu "risk on" pasar seiring The Fed tahan suku bunga</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 23:34:21 +0700</t>
+          <t>Thu, 30 Jul 2026 09:48:24 +0700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 tinggal menghitung hari. ...</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis bergerak menguat dipicu oleh sikap risk ...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5673507/20-ide-tema-17-agustus-2026-yang-kreatif-unik-dan-penuh-makna-untuk-hut-ke-81-ri</t>
+          <t>https://www.antaranews.com/berita/5672087/ihsg-menguat-dipicu-risk-on-pasar-seiring-the-fed-tahan-suku-bunga</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/IMG-20260630-WA0035.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-270726-dr-05.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -549,33 +549,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ekonomi, otomotif</t>
+          <t>politik</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6 titik shuttle bus gratis GIIAS 2026 ke ICE BSD, cek lokasi &amp; jadwalnya</t>
+          <t>20 ide tema 17 Agustus 2026 yang kreatif, unik, dan penuh makna untuk HUT ke-81 RI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 18:17:21 +0700</t>
+          <t>Thu, 30 Jul 2026 23:34:21 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Penyelenggara GAIKINDO Indonesia International Auto Show (GIIAS) 2026 kembali menyediakan layanan shuttle bus gratis ...</t>
+          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 tinggal menghitung hari. ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5672876/6-titik-shuttle-bus-gratis-giias-2026-ke-ice-bsd-cek-lokasi-jadwalnya</t>
+          <t>https://www.antaranews.com/berita/5673507/20-ide-tema-17-agustus-2026-yang-kreatif-unik-dan-penuh-makna-untuk-hut-ke-81-ri</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/IMG_1404.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/IMG-20260630-WA0035.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -587,33 +587,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi, otomotif</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PU uji coba irigasi Pante Lhong Aceh untuk aliri 6.562 hektare sawah</t>
+          <t>6 titik shuttle bus gratis GIIAS 2026 ke ICE BSD, cek lokasi &amp; jadwalnya</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 17:28:11 +0700</t>
+          <t>Thu, 30 Jul 2026 18:17:21 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Menteri Pekerjaan Umum (PU) Dody Hanggodo melakukan uji coba irigasi Pante Lhong Kabupaten Bireuen, Aceh yang telah ...</t>
+          <t>Penyelenggara GAIKINDO Indonesia International Auto Show (GIIAS) 2026 kembali menyediakan layanan shuttle bus gratis ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672783/pu-uji-coba-irigasi-pante-lhong-aceh-untuk-aliri-6562-hektare-sawah</t>
+          <t>https://otomotif.antaranews.com/berita/5672876/6-titik-shuttle-bus-gratis-giias-2026-ke-ice-bsd-cek-lokasi-jadwalnya</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG-20260730-WA0014_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/IMG_1404.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -630,28 +630,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IHSG ditutup menguat ditopang musim laporan keuangan emiten</t>
+          <t>PU uji coba irigasi Pante Lhong Aceh untuk aliri 6.562 hektare sawah</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 17:05:56 +0700</t>
+          <t>Thu, 30 Jul 2026 17:28:11 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis sore ditutup menguat ditopang oleh musim ...</t>
+          <t>Menteri Pekerjaan Umum (PU) Dody Hanggodo melakukan uji coba irigasi Pante Lhong Kabupaten Bireuen, Aceh yang telah ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672741/ihsg-ditutup-menguat-ditopang-musim-laporan-keuangan-emiten</t>
+          <t>https://www.antaranews.com/berita/5672783/pu-uji-coba-irigasi-pante-lhong-aceh-untuk-aliri-6562-hektare-sawah</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/pembukaan-ihsg-usai-libur-lebaran-2760782.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG-20260730-WA0014_1.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -668,28 +668,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OJK tuntaskan pemeriksaan 17 kasus manipulasi di pasar modal</t>
+          <t>IHSG ditutup menguat ditopang musim laporan keuangan emiten</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:26:08 +0700</t>
+          <t>Thu, 30 Jul 2026 17:05:56 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan telah menyelesaikan pemeriksaan atas sebanyak 17 kasus terkait pelanggaran ...</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis sore ditutup menguat ditopang oleh musim ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672663/ojk-tuntaskan-pemeriksaan-17-kasus-manipulasi-di-pasar-modal</t>
+          <t>https://www.antaranews.com/berita/5672741/ihsg-ditutup-menguat-ditopang-musim-laporan-keuangan-emiten</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/WhatsApp-Image-2026-06-30-at-18.00.00.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/pembukaan-ihsg-usai-libur-lebaran-2760782.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -706,28 +706,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OJK ungkap 7 manajer investasi andil peluncuran ETF Emas di 10 Agustus</t>
+          <t>OJK tuntaskan pemeriksaan 17 kasus manipulasi di pasar modal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:07:07 +0700</t>
+          <t>Thu, 30 Jul 2026 16:26:08 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan sebanyak lima sampai tujuh Manajer Investasi (MI) akan turut berpartisipasi ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan telah menyelesaikan pemeriksaan atas sebanyak 17 kasus terkait pelanggaran ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672456/ojk-ungkap-7-manajer-investasi-andil-peluncuran-etf-emas-di-10-agustus</t>
+          <t>https://www.antaranews.com/berita/5672663/ojk-tuntaskan-pemeriksaan-17-kasus-manipulasi-di-pasar-modal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/06/IMG-20260406-WA0035_copy_1280x732.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/WhatsApp-Image-2026-06-30-at-18.00.00.jpeg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -744,28 +744,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>United Tractors cetak pendapatan Rp58,3 triliun di semester I-2026</t>
+          <t>OJK ungkap 7 manajer investasi andil peluncuran ETF Emas di 10 Agustus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 12:29:10 +0700</t>
+          <t>Thu, 30 Jul 2026 14:07:07 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Perusahaan grup PT Astra International Tbk (ASII) yaitu PT United Tractors Tbk (UNTR) membukukan pendapatan bersih ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan sebanyak lima sampai tujuh Manajer Investasi (MI) akan turut berpartisipasi ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672283/united-tractors-cetak-pendapatan-rp583-triliun-di-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5672456/ojk-ungkap-7-manajer-investasi-andil-peluncuran-etf-emas-di-10-agustus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/16/1000566369_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/06/IMG-20260406-WA0035_copy_1280x732.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -782,28 +782,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IHSG menguat dipicu "risk on" pasar seiring The Fed tahan suku bunga</t>
+          <t>United Tractors cetak pendapatan Rp58,3 triliun di semester I-2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 09:48:24 +0700</t>
+          <t>Thu, 30 Jul 2026 12:29:10 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis bergerak menguat dipicu oleh sikap risk ...</t>
+          <t>Perusahaan grup PT Astra International Tbk (ASII) yaitu PT United Tractors Tbk (UNTR) membukukan pendapatan bersih ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672087/ihsg-menguat-dipicu-risk-on-pasar-seiring-the-fed-tahan-suku-bunga</t>
+          <t>https://www.antaranews.com/berita/5672283/united-tractors-cetak-pendapatan-rp583-triliun-di-semester-i-2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-270726-dr-05.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/16/1000566369_1.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/data/berita_antara_2026-07-30.xlsx
+++ b/data/berita_antara_2026-07-30.xlsx
@@ -549,33 +549,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>politik</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20 ide tema 17 Agustus 2026 yang kreatif, unik, dan penuh makna untuk HUT ke-81 RI</t>
+          <t>United Tractors cetak pendapatan Rp58,3 triliun di semester I-2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 23:34:21 +0700</t>
+          <t>Thu, 30 Jul 2026 12:29:10 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 tinggal menghitung hari. ...</t>
+          <t>Perusahaan grup PT Astra International Tbk (ASII) yaitu PT United Tractors Tbk (UNTR) membukukan pendapatan bersih ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5673507/20-ide-tema-17-agustus-2026-yang-kreatif-unik-dan-penuh-makna-untuk-hut-ke-81-ri</t>
+          <t>https://www.antaranews.com/berita/5672283/united-tractors-cetak-pendapatan-rp583-triliun-di-semester-i-2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/IMG-20260630-WA0035.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/16/1000566369_1.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -587,33 +587,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ekonomi, otomotif</t>
+          <t>politik</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6 titik shuttle bus gratis GIIAS 2026 ke ICE BSD, cek lokasi &amp; jadwalnya</t>
+          <t>20 ide tema 17 Agustus 2026 yang kreatif, unik, dan penuh makna untuk HUT ke-81 RI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 18:17:21 +0700</t>
+          <t>Thu, 30 Jul 2026 23:34:21 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penyelenggara GAIKINDO Indonesia International Auto Show (GIIAS) 2026 kembali menyediakan layanan shuttle bus gratis ...</t>
+          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 tinggal menghitung hari. ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5672876/6-titik-shuttle-bus-gratis-giias-2026-ke-ice-bsd-cek-lokasi-jadwalnya</t>
+          <t>https://www.antaranews.com/berita/5673507/20-ide-tema-17-agustus-2026-yang-kreatif-unik-dan-penuh-makna-untuk-hut-ke-81-ri</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/IMG_1404.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/IMG-20260630-WA0035.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -625,33 +625,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi, otomotif</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PU uji coba irigasi Pante Lhong Aceh untuk aliri 6.562 hektare sawah</t>
+          <t>6 titik shuttle bus gratis GIIAS 2026 ke ICE BSD, cek lokasi &amp; jadwalnya</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 17:28:11 +0700</t>
+          <t>Thu, 30 Jul 2026 18:17:21 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Menteri Pekerjaan Umum (PU) Dody Hanggodo melakukan uji coba irigasi Pante Lhong Kabupaten Bireuen, Aceh yang telah ...</t>
+          <t>Penyelenggara GAIKINDO Indonesia International Auto Show (GIIAS) 2026 kembali menyediakan layanan shuttle bus gratis ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672783/pu-uji-coba-irigasi-pante-lhong-aceh-untuk-aliri-6562-hektare-sawah</t>
+          <t>https://otomotif.antaranews.com/berita/5672876/6-titik-shuttle-bus-gratis-giias-2026-ke-ice-bsd-cek-lokasi-jadwalnya</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG-20260730-WA0014_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/IMG_1404.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -668,28 +668,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IHSG ditutup menguat ditopang musim laporan keuangan emiten</t>
+          <t>PU uji coba irigasi Pante Lhong Aceh untuk aliri 6.562 hektare sawah</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 17:05:56 +0700</t>
+          <t>Thu, 30 Jul 2026 17:28:11 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis sore ditutup menguat ditopang oleh musim ...</t>
+          <t>Menteri Pekerjaan Umum (PU) Dody Hanggodo melakukan uji coba irigasi Pante Lhong Kabupaten Bireuen, Aceh yang telah ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672741/ihsg-ditutup-menguat-ditopang-musim-laporan-keuangan-emiten</t>
+          <t>https://www.antaranews.com/berita/5672783/pu-uji-coba-irigasi-pante-lhong-aceh-untuk-aliri-6562-hektare-sawah</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/pembukaan-ihsg-usai-libur-lebaran-2760782.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG-20260730-WA0014_1.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -706,28 +706,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OJK tuntaskan pemeriksaan 17 kasus manipulasi di pasar modal</t>
+          <t>IHSG ditutup menguat ditopang musim laporan keuangan emiten</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:26:08 +0700</t>
+          <t>Thu, 30 Jul 2026 17:05:56 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan telah menyelesaikan pemeriksaan atas sebanyak 17 kasus terkait pelanggaran ...</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis sore ditutup menguat ditopang oleh musim ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672663/ojk-tuntaskan-pemeriksaan-17-kasus-manipulasi-di-pasar-modal</t>
+          <t>https://www.antaranews.com/berita/5672741/ihsg-ditutup-menguat-ditopang-musim-laporan-keuangan-emiten</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/WhatsApp-Image-2026-06-30-at-18.00.00.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/pembukaan-ihsg-usai-libur-lebaran-2760782.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -744,28 +744,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OJK ungkap 7 manajer investasi andil peluncuran ETF Emas di 10 Agustus</t>
+          <t>OJK tuntaskan pemeriksaan 17 kasus manipulasi di pasar modal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:07:07 +0700</t>
+          <t>Thu, 30 Jul 2026 16:26:08 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan sebanyak lima sampai tujuh Manajer Investasi (MI) akan turut berpartisipasi ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan telah menyelesaikan pemeriksaan atas sebanyak 17 kasus terkait pelanggaran ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672456/ojk-ungkap-7-manajer-investasi-andil-peluncuran-etf-emas-di-10-agustus</t>
+          <t>https://www.antaranews.com/berita/5672663/ojk-tuntaskan-pemeriksaan-17-kasus-manipulasi-di-pasar-modal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/06/IMG-20260406-WA0035_copy_1280x732.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/WhatsApp-Image-2026-06-30-at-18.00.00.jpeg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -782,28 +782,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>United Tractors cetak pendapatan Rp58,3 triliun di semester I-2026</t>
+          <t>OJK ungkap 7 manajer investasi andil peluncuran ETF Emas di 10 Agustus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 12:29:10 +0700</t>
+          <t>Thu, 30 Jul 2026 14:07:07 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Perusahaan grup PT Astra International Tbk (ASII) yaitu PT United Tractors Tbk (UNTR) membukukan pendapatan bersih ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan sebanyak lima sampai tujuh Manajer Investasi (MI) akan turut berpartisipasi ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672283/united-tractors-cetak-pendapatan-rp583-triliun-di-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5672456/ojk-ungkap-7-manajer-investasi-andil-peluncuran-etf-emas-di-10-agustus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/16/1000566369_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/06/IMG-20260406-WA0035_copy_1280x732.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/data/berita_antara_2026-07-30.xlsx
+++ b/data/berita_antara_2026-07-30.xlsx
@@ -587,33 +587,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>politik</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20 ide tema 17 Agustus 2026 yang kreatif, unik, dan penuh makna untuk HUT ke-81 RI</t>
+          <t>PU uji coba irigasi Pante Lhong Aceh untuk aliri 6.562 hektare sawah</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 23:34:21 +0700</t>
+          <t>Thu, 30 Jul 2026 17:28:11 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 tinggal menghitung hari. ...</t>
+          <t>Menteri Pekerjaan Umum (PU) Dody Hanggodo melakukan uji coba irigasi Pante Lhong Kabupaten Bireuen, Aceh yang telah ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5673507/20-ide-tema-17-agustus-2026-yang-kreatif-unik-dan-penuh-makna-untuk-hut-ke-81-ri</t>
+          <t>https://www.antaranews.com/berita/5672783/pu-uji-coba-irigasi-pante-lhong-aceh-untuk-aliri-6562-hektare-sawah</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/IMG-20260630-WA0035.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG-20260730-WA0014_1.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -625,33 +625,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ekonomi, otomotif</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6 titik shuttle bus gratis GIIAS 2026 ke ICE BSD, cek lokasi &amp; jadwalnya</t>
+          <t>IHSG ditutup menguat ditopang musim laporan keuangan emiten</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 18:17:21 +0700</t>
+          <t>Thu, 30 Jul 2026 17:05:56 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penyelenggara GAIKINDO Indonesia International Auto Show (GIIAS) 2026 kembali menyediakan layanan shuttle bus gratis ...</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis sore ditutup menguat ditopang oleh musim ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5672876/6-titik-shuttle-bus-gratis-giias-2026-ke-ice-bsd-cek-lokasi-jadwalnya</t>
+          <t>https://www.antaranews.com/berita/5672741/ihsg-ditutup-menguat-ditopang-musim-laporan-keuangan-emiten</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/IMG_1404.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/pembukaan-ihsg-usai-libur-lebaran-2760782.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -668,28 +668,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PU uji coba irigasi Pante Lhong Aceh untuk aliri 6.562 hektare sawah</t>
+          <t>OJK tuntaskan pemeriksaan 17 kasus manipulasi di pasar modal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 17:28:11 +0700</t>
+          <t>Thu, 30 Jul 2026 16:26:08 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Menteri Pekerjaan Umum (PU) Dody Hanggodo melakukan uji coba irigasi Pante Lhong Kabupaten Bireuen, Aceh yang telah ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan telah menyelesaikan pemeriksaan atas sebanyak 17 kasus terkait pelanggaran ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672783/pu-uji-coba-irigasi-pante-lhong-aceh-untuk-aliri-6562-hektare-sawah</t>
+          <t>https://www.antaranews.com/berita/5672663/ojk-tuntaskan-pemeriksaan-17-kasus-manipulasi-di-pasar-modal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG-20260730-WA0014_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/WhatsApp-Image-2026-06-30-at-18.00.00.jpeg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -706,28 +706,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IHSG ditutup menguat ditopang musim laporan keuangan emiten</t>
+          <t>OJK ungkap 7 manajer investasi andil peluncuran ETF Emas di 10 Agustus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 17:05:56 +0700</t>
+          <t>Thu, 30 Jul 2026 14:07:07 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis sore ditutup menguat ditopang oleh musim ...</t>
+          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan sebanyak lima sampai tujuh Manajer Investasi (MI) akan turut berpartisipasi ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672741/ihsg-ditutup-menguat-ditopang-musim-laporan-keuangan-emiten</t>
+          <t>https://www.antaranews.com/berita/5672456/ojk-ungkap-7-manajer-investasi-andil-peluncuran-etf-emas-di-10-agustus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/pembukaan-ihsg-usai-libur-lebaran-2760782.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/06/IMG-20260406-WA0035_copy_1280x732.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -739,33 +739,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>politik</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OJK tuntaskan pemeriksaan 17 kasus manipulasi di pasar modal</t>
+          <t>20 ide tema 17 Agustus 2026 yang kreatif, unik, dan penuh makna untuk HUT ke-81 RI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 16:26:08 +0700</t>
+          <t>Thu, 30 Jul 2026 23:34:21 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan telah menyelesaikan pemeriksaan atas sebanyak 17 kasus terkait pelanggaran ...</t>
+          <t>Perayaan Hari Ulang Tahun (HUT) ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 tinggal menghitung hari. ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672663/ojk-tuntaskan-pemeriksaan-17-kasus-manipulasi-di-pasar-modal</t>
+          <t>https://www.antaranews.com/berita/5673507/20-ide-tema-17-agustus-2026-yang-kreatif-unik-dan-penuh-makna-untuk-hut-ke-81-ri</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/WhatsApp-Image-2026-06-30-at-18.00.00.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/30/IMG-20260630-WA0035.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -777,33 +777,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi, otomotif</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OJK ungkap 7 manajer investasi andil peluncuran ETF Emas di 10 Agustus</t>
+          <t>6 titik shuttle bus gratis GIIAS 2026 ke ICE BSD, cek lokasi &amp; jadwalnya</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thu, 30 Jul 2026 14:07:07 +0700</t>
+          <t>Thu, 30 Jul 2026 18:17:21 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan sebanyak lima sampai tujuh Manajer Investasi (MI) akan turut berpartisipasi ...</t>
+          <t>Penyelenggara GAIKINDO Indonesia International Auto Show (GIIAS) 2026 kembali menyediakan layanan shuttle bus gratis ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5672456/ojk-ungkap-7-manajer-investasi-andil-peluncuran-etf-emas-di-10-agustus</t>
+          <t>https://otomotif.antaranews.com/berita/5672876/6-titik-shuttle-bus-gratis-giias-2026-ke-ice-bsd-cek-lokasi-jadwalnya</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/04/06/IMG-20260406-WA0035_copy_1280x732.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/IMG_1404.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
